--- a/output/pdf_financials_xlsx/ASM.xlsx
+++ b/output/pdf_financials_xlsx/ASM.xlsx
@@ -8032,25 +8032,25 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-2.387771</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.901912</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-11.853024</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-19.628309</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-4.81</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-5.527</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-5.361</v>
       </c>
       <c r="N118" s="1" t="inlineStr">
         <is>
@@ -8058,19 +8058,19 @@
         </is>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.294</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-1.131</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.156</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-2.105</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-0.576</v>
       </c>
     </row>
     <row r="119">
@@ -41474,7 +41474,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -45532,7 +45536,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E353" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ASM.xlsx
+++ b/output/pdf_financials_xlsx/ASM.xlsx
@@ -1151,19 +1151,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.359339</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.146386</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.06822400000000001</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.014206</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.078857</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -2228,19 +2228,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.386946</v>
+        <v>-1.746285</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.440223</v>
+        <v>-1.586609</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.227321</v>
+        <v>-1.295545</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.763163</v>
+        <v>-0.777369</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.097853</v>
+        <v>-4.17671</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.002857</v>
@@ -2354,19 +2354,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.386946</v>
+        <v>-1.746285</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.440223</v>
+        <v>-1.586609</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.227321</v>
+        <v>-1.295545</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.759329</v>
+        <v>-0.773535</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.09705</v>
+        <v>-4.175907</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.002857</v>
@@ -2707,34 +2707,34 @@
         <v>4.249794</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>7.475134</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>5.401109</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>11.78</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.252</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>24.765</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>11.245</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>27.317</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>101.724</v>
       </c>
     </row>
     <row r="35">
@@ -2833,34 +2833,34 @@
         <v>4.249794</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>7.475134</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>13.427</v>
+        <v>18.828109</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>10</v>
+        <v>21.78</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>1</v>
+        <v>4.252</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>9.625</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>24.765</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>11.245</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>2.688</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>27.317</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>101.724</v>
       </c>
     </row>
     <row r="37">
@@ -3589,34 +3589,34 @@
         <v>2.471217</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>11.705222</v>
+        <v>4.230088</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>16.274</v>
+        <v>4.494</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>8.625</v>
+        <v>5.373</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>15.702</v>
+        <v>6.077</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>29.091</v>
+        <v>4.326</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>16.653</v>
+        <v>5.408</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>11.406</v>
+        <v>8.718</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>29.808</v>
+        <v>2.491</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>107.869</v>
+        <v>6.145</v>
       </c>
     </row>
     <row r="49">
@@ -8410,25 +8410,25 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.042969</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.335531</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.943678</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-1.216497</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-1.531</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-1.581</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-1.166</v>
       </c>
       <c r="N124" s="1" t="inlineStr">
         <is>
@@ -8436,10 +8436,10 @@
         </is>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.477</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-1.179</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>0</v>
@@ -8473,25 +8473,25 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.042969</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.335531</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.943678</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-1.216497</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-1.531</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-1.581</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-1.166</v>
       </c>
       <c r="N125" s="1" t="inlineStr">
         <is>
@@ -8499,10 +8499,10 @@
         </is>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.477</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-1.179</v>
       </c>
       <c r="Q125" s="3" t="n">
         <v>0</v>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -16126,7 +16126,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -45218,7 +45218,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -47602,7 +47606,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -58906,7 +58914,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -66880,7 +66888,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -71224,7 +71232,7 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
@@ -76742,7 +76750,7 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
@@ -78218,7 +78226,7 @@
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E669" s="5" t="n">

--- a/output/pdf_financials_xlsx/ASM.xlsx
+++ b/output/pdf_financials_xlsx/ASM.xlsx
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.5010829999999999</v>
+        <v>-0.5010829999999999</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0.098653</v>
@@ -1494,15 +1494,13 @@
         <v>4.439</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>2.771</v>
+        <v>-0.14</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="N17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.645</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>-0.96</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>0.439</v>
@@ -2544,10 +2542,10 @@
         <v>68.76839659178931</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>52.35216323446061</v>
+        <v>2.645002833931608</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>20.01967535661584</v>
+        <v>31.72651254303984</v>
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
@@ -5013,40 +5011,40 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.5858449999999999</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>1.292326</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>1.815747</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>1.311956</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>1.435</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>1.476</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>2.632</v>
       </c>
     </row>
     <row r="71">
@@ -5076,40 +5074,40 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.5858449999999999</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>1.292326</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>1.815747</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>1.311956</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>1.435</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.389</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.971</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>1.476</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>2.632</v>
       </c>
     </row>
     <row r="72">
@@ -5328,40 +5326,40 @@
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.785225</v>
+        <v>0.19938</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2.507502</v>
+        <v>1.215176</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>9.865645000000001</v>
+        <v>8.049898000000001</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>7.128361</v>
+        <v>5.816405</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>8.095000000000001</v>
+        <v>6.66</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>3.956</v>
+        <v>3.006</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>4.655</v>
+        <v>3.963</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.583</v>
+        <v>0.194</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>7.295</v>
+        <v>6.324</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>1.941</v>
+        <v>0.291</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>5.242</v>
+        <v>3.766</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>18.302</v>
+        <v>15.67</v>
       </c>
     </row>
     <row r="76">
@@ -5654,65 +5652,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.02386622934556477</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.02868623271216447</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.0349594239932733</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.03495942385789967</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.02322231931902774</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.01263835674755215</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.01283311388461325</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.004954972168086922</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.009906040542332765</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.01556589088782181</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.01177042879129818</v>
+      </c>
+      <c r="S80" s="3" t="n">
+        <v>0.01124642139896594</v>
       </c>
     </row>
     <row r="81">
@@ -11052,7 +11026,11 @@
           <t>Current portion of finance lease obligations</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -14756,7 +14734,11 @@
           <t>Current portion of finance lease obligations 15</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -17932,7 +17914,11 @@
           <t>Current portion of finance lease obligations 15 950</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -21520,7 +21506,11 @@
           <t>Current portion of finance lease obligations 16 1,116,377</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -25272,7 +25262,11 @@
           <t>Current portion of finance lease obligations 17</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -27414,7 +27408,11 @@
           <t>Current portion of finance lease obligations 21</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -39466,7 +39464,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -42146,7 +42148,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -43970,7 +43976,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -44074,7 +44084,11 @@
           <t>Deferred income tax expense 24</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -48418,7 +48432,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -52358,7 +52376,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -63384,7 +63406,11 @@
           <t>Current income tax recovery (expense) 24</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E526" t="inlineStr">
         <is>
           <t>-</t>
@@ -63488,7 +63514,11 @@
           <t>Deferred income tax recovery (expense) 24</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E527" t="inlineStr">
         <is>
           <t>-</t>
@@ -63592,7 +63622,11 @@
           <t>Income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr"/>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
           <t>-</t>
@@ -65670,7 +65704,11 @@
           <t>Deferred income tax recovery 27</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E548" t="inlineStr">
         <is>
           <t>-</t>
@@ -67308,7 +67346,11 @@
           <t>Deferred income tax recovery (expense) 27</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr"/>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E564" t="inlineStr">
         <is>
           <t>-</t>
@@ -69882,7 +69924,11 @@
           <t>Deferred income tax recovery (expense) 26</t>
         </is>
       </c>
-      <c r="D589" t="inlineStr"/>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E589" t="inlineStr">
         <is>
           <t>-</t>
@@ -72180,7 +72226,11 @@
           <t>Deferred income tax recovery (expense) 28</t>
         </is>
       </c>
-      <c r="D611" t="inlineStr"/>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E611" t="inlineStr">
         <is>
           <t>-</t>
@@ -81680,7 +81730,11 @@
           <t>Future income tax recovery (expense) (Note 17)</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E702" s="5" t="n">
         <v>0.5010829999999999</v>
       </c>
